--- a/CD_exec/data/misc/ICPSR NIBRS Codes.xlsx
+++ b/CD_exec/data/misc/ICPSR NIBRS Codes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti369\Dropbox\Card and Dahl Replication\Github Repo\raw_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti369\Dropbox\Card and Dahl Replication\rep - CD executable\data\misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94434A6-EE16-4C8F-BE1D-9A5225F34792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1398060F-B391-4C11-8515-3A12DB9A22DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{36B491CC-B509-4531-B61A-605A04F5F4B7}"/>
+    <workbookView xWindow="-26850" yWindow="3360" windowWidth="21600" windowHeight="12585" xr2:uid="{36B491CC-B509-4531-B61A-605A04F5F4B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -182,11 +182,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -195,6 +192,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -511,354 +514,358 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC16A1F2-8724-455F-B9D1-2CBFDFD7933C}">
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="2"/>
-    <col min="2" max="2" width="9.1796875" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.81640625" style="2"/>
+    <col min="1" max="1" width="8.85546875" style="3"/>
+    <col min="2" max="2" width="9.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="3"/>
+    <col min="4" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4">
+    <row r="2" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>1995</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="6">
         <v>22880</v>
       </c>
-      <c r="C2" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
+      <c r="C2" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>1996</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <v>22881</v>
       </c>
-      <c r="C3" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>1997</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>22882</v>
       </c>
-      <c r="C4" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
         <v>1998</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>22883</v>
       </c>
-      <c r="C5" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>1999</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <v>22884</v>
       </c>
-      <c r="C6" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>2000</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>2001</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>2002</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>2003</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <v>2004</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
         <v>2005</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <v>2006</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
         <v>2007</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
+    <row r="15" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>2008</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
+      <c r="C15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <v>2009</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="4" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <v>2010</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
         <v>2011</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
+      <c r="C18" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <v>2012</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
+      <c r="C19" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
         <v>2013</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
+      <c r="C20" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
         <v>2014</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
+      <c r="C21" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
         <v>2015</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
+      <c r="C22" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <v>2016</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4">
+      <c r="C23" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
         <v>2017</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
+      <c r="C24" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
         <v>2018</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
+    <row r="26" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
         <v>2019</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4">
+      <c r="C26" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
         <v>2020</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4">
+      <c r="C27" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
         <v>2021</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4">
+    <row r="29" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
         <v>2022</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4">
+    <row r="30" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
         <v>2023</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="4">
+    <row r="31" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
         <v>2024</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <v>1</v>
       </c>
+    </row>
+    <row r="32" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -869,12 +876,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE6B1D5B-70A8-4671-B439-A50FDEB17BAE}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -891,14 +898,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
       <c r="B2">
         <v>13</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>42735</v>
       </c>
       <c r="D2">
@@ -908,14 +915,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
       <c r="B3">
         <v>14</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>42735</v>
       </c>
       <c r="D3">
@@ -925,14 +932,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
       <c r="B4">
         <v>15</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>42735</v>
       </c>
       <c r="D4">
@@ -942,14 +949,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>32</v>
       </c>
       <c r="B5">
         <v>16</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>42735</v>
       </c>
       <c r="D5">
@@ -959,14 +966,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
       <c r="B6">
         <v>17</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>42735</v>
       </c>
       <c r="D6">
@@ -976,14 +983,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
       <c r="B7">
         <v>18</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>42735</v>
       </c>
       <c r="D7">
@@ -993,14 +1000,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
       <c r="B8">
         <v>19</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>42735</v>
       </c>
       <c r="D8">
@@ -1010,14 +1017,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
       <c r="B9">
         <v>21</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>42735</v>
       </c>
       <c r="D9">
@@ -1027,14 +1034,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
       <c r="B10">
         <v>22</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>42735</v>
       </c>
       <c r="D10">
@@ -1044,14 +1051,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
       <c r="B11">
         <v>23</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>42735</v>
       </c>
       <c r="D11">
@@ -1061,14 +1068,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>42736</v>
       </c>
       <c r="D12">
@@ -1078,14 +1085,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>42736</v>
       </c>
       <c r="D13">
@@ -1095,14 +1102,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>42736</v>
       </c>
       <c r="D14">
@@ -1112,14 +1119,14 @@
         <v>20819</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>42736</v>
       </c>
       <c r="D15">
@@ -1129,14 +1136,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
       <c r="B16">
         <v>10</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>42736</v>
       </c>
       <c r="D16">
@@ -1146,14 +1153,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
       <c r="B17">
         <v>12</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>42736</v>
       </c>
       <c r="D17">
@@ -1163,14 +1170,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
       <c r="B18">
         <v>13</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>42736</v>
       </c>
       <c r="D18">
@@ -1180,14 +1187,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
       <c r="B19">
         <v>14</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>42736</v>
       </c>
       <c r="D19">
@@ -1197,14 +1204,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
       <c r="B20">
         <v>15</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <v>42736</v>
       </c>
       <c r="D20">
@@ -1214,14 +1221,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21">
         <v>16</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>42736</v>
       </c>
       <c r="D21">
@@ -1231,14 +1238,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>32</v>
       </c>
       <c r="B22">
         <v>17</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <v>42736</v>
       </c>
       <c r="D22">
@@ -1248,14 +1255,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>32</v>
       </c>
       <c r="B23">
         <v>18</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="2">
         <v>42736</v>
       </c>
       <c r="D23">
@@ -1265,14 +1272,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
       <c r="B24">
         <v>20</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="2">
         <v>42736</v>
       </c>
       <c r="D24">
@@ -1282,14 +1289,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
       <c r="B25">
         <v>21</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="2">
         <v>42736</v>
       </c>
       <c r="D25">
@@ -1299,14 +1306,14 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>32</v>
       </c>
       <c r="B26">
         <v>22</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="2">
         <v>42736</v>
       </c>
       <c r="D26">
